--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4398" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4398" uniqueCount="712">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2137,6 +2137,10 @@
   </si>
   <si>
     <t>antimicrobialSusceptibilityObservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
   </si>
   <si>
     <t>Observation.derivedFrom</t>
@@ -14009,7 +14013,7 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>651</v>
@@ -14103,10 +14107,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14129,16 +14133,16 @@
         <v>93</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14188,7 +14192,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14212,7 +14216,7 @@
         <v>655</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -14223,10 +14227,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14252,16 +14256,16 @@
         <v>596</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14310,7 +14314,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14331,10 +14335,10 @@
         <v>20</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14345,10 +14349,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14463,10 +14467,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14583,10 +14587,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14705,10 +14709,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14734,13 +14738,13 @@
         <v>238</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>339</v>
@@ -14771,10 +14775,10 @@
         <v>158</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>20</v>
@@ -14792,7 +14796,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>92</v>
@@ -14810,7 +14814,7 @@
         <v>20</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>344</v>
@@ -14827,10 +14831,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14856,13 +14860,13 @@
         <v>497</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>501</v>
@@ -14914,7 +14918,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14932,7 +14936,7 @@
         <v>20</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>505</v>
@@ -14949,10 +14953,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14978,13 +14982,13 @@
         <v>509</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>513</v>
@@ -15036,7 +15040,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15045,7 +15049,7 @@
         <v>92</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>104</v>
@@ -15071,10 +15075,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15100,7 +15104,7 @@
         <v>238</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>521</v>
@@ -15158,7 +15162,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15193,10 +15197,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15222,13 +15226,13 @@
         <v>596</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O105" t="s" s="2">
         <v>600</v>
@@ -15280,7 +15284,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15315,10 +15319,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15433,10 +15437,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15553,10 +15557,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15675,10 +15679,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15793,10 +15797,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15911,10 +15915,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15980,7 +15984,7 @@
         <v>628</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -16033,10 +16037,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16102,7 +16106,7 @@
         <v>637</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>20</v>
@@ -16155,10 +16159,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16275,10 +16279,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -633,7 +633,7 @@
     <t>valueAttachment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/ig/StructureDefinition/value-attachment-314e}
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/observation-valueAttachment}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Observation.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -920,7 +920,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -949,7 +949,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|MedicationStatement|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1439,7 +1439,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1470,7 +1470,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1493,7 +1493,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1592,7 +1592,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1872,7 +1872,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1900,7 +1900,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|DeviceMetric) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2146,7 +2146,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microorganism-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
